--- a/tests/SafeOpenXml.Tests/Examples/WorkbookProtection/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/WorkbookProtection/output.xlsx
@@ -3,7 +3,7 @@
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:workbookProtection workbookPassword="C258" lockStructure="1"/>
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Reeb17450a3394536"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2e479c6316d64d96"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/WorkbookProtection/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/WorkbookProtection/output.xlsx
@@ -3,7 +3,7 @@
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:workbookProtection workbookPassword="C258" lockStructure="1"/>
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2e479c6316d64d96"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R38e896ea33e3419e"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/WorkbookProtection/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/WorkbookProtection/output.xlsx
@@ -3,7 +3,7 @@
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:workbookProtection workbookPassword="C258" lockStructure="1"/>
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R38e896ea33e3419e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1475934775d141f0"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/WorkbookProtection/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/WorkbookProtection/output.xlsx
@@ -3,7 +3,7 @@
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:workbookProtection workbookPassword="C258" lockStructure="1"/>
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1475934775d141f0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd2f76614cee94cb4"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/WorkbookProtection/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/WorkbookProtection/output.xlsx
@@ -3,7 +3,7 @@
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:workbookProtection workbookPassword="C258" lockStructure="1"/>
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd2f76614cee94cb4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf9bdaf6c845540e3"/>
   </x:sheets>
 </x:workbook>
 </file>
